--- a/apps/excel-service/templates/XANSHA/HOTEL/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Completed Work Certificates.xlsx
@@ -1,40 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="TDSheet" sheetId="1" r:id="rId5"/>
+    <sheet name="TDSheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve">Приложение </t>
   </si>
   <si>
-    <t>к приказу Министра финансов</t>
+    <t xml:space="preserve">к приказу Министра финансов</t>
   </si>
   <si>
-    <t>Республики Казахстан</t>
+    <t xml:space="preserve">Республики Казахстан</t>
   </si>
   <si>
     <t>от</t>
   </si>
   <si>
-    <t>27 октября года 2014 года № 458</t>
+    <t xml:space="preserve">27 октября года 2014 года № 458</t>
   </si>
   <si>
-    <t>Приложение 50</t>
+    <t xml:space="preserve">Приложение 50</t>
   </si>
   <si>
-    <t>от 20 декабря 2012 года № 562</t>
+    <t xml:space="preserve">от 20 декабря 2012 года № 562</t>
   </si>
   <si>
-    <t>Форма Р-1</t>
+    <t xml:space="preserve">Форма Р-1</t>
   </si>
   <si>
     <t>ИИН/БИН</t>
@@ -59,22 +64,22 @@
     <t xml:space="preserve">Индивидуальный предприниматель гостиница "XANSHA" Рыспаева Гаухар Сериковна,                                                               область Улытау  п.Жанаарка, Жанааркинский район </t>
   </si>
   <si>
-    <t>полное наименование, адрес, данные о средствах связи</t>
+    <t xml:space="preserve">полное наименование, адрес, данные о средствах связи</t>
   </si>
   <si>
     <t xml:space="preserve">Договор (контракт) </t>
   </si>
   <si>
-    <t>№{enumeration} от  {documentDate.0}г</t>
+    <t xml:space="preserve">№{enumeration} от  {documentDate.0}г</t>
   </si>
   <si>
-    <t>Номер документа</t>
+    <t xml:space="preserve">Номер документа</t>
   </si>
   <si>
-    <t>Дата составления</t>
+    <t xml:space="preserve">Дата составления</t>
   </si>
   <si>
-    <t>АКТ ВЫПОЛНЕННЫХ РАБОТ (ОКАЗАННЫХ УСЛУГ)</t>
+    <t xml:space="preserve">АКТ ВЫПОЛНЕННЫХ РАБОТ (ОКАЗАННЫХ УСЛУГ)</t>
   </si>
   <si>
     <t>{enumeration}</t>
@@ -83,28 +88,28 @@
     <t>{documentDate.1}</t>
   </si>
   <si>
-    <t>Номер по порядку</t>
+    <t xml:space="preserve">Номер по порядку</t>
   </si>
   <si>
-    <t>Наименование работ (услуг) (в разрезе их подвидов в соответствии с технической спецификацией, заданием, графиком выполнения работ (услуг) при их наличии)</t>
+    <t xml:space="preserve">Наименование работ (услуг) (в разрезе их подвидов в соответствии с технической спецификацией, заданием, графиком выполнения работ (услуг) при их наличии)</t>
   </si>
   <si>
-    <t>Дата выполнения работ (оказания услуг)</t>
+    <t xml:space="preserve">Дата выполнения работ (оказания услуг)</t>
   </si>
   <si>
-    <t>Сведения об отчете о научных исследованиях, маркетинговых, консультационных и прочих услугах (дата, номер, количество страниц) (при их наличии)</t>
+    <t xml:space="preserve">Сведения об отчете о научных исследованиях, маркетинговых, консультационных и прочих услугах (дата, номер, количество страниц) (при их наличии)</t>
   </si>
   <si>
-    <t>Единица измерения</t>
+    <t xml:space="preserve">Единица измерения</t>
   </si>
   <si>
-    <t>Выполнено работ (оказано услуг)</t>
+    <t xml:space="preserve">Выполнено работ (оказано услуг)</t>
   </si>
   <si>
     <t>количество</t>
   </si>
   <si>
-    <t>цена за единицу</t>
+    <t xml:space="preserve">цена за единицу</t>
   </si>
   <si>
     <t>стоимость</t>
@@ -115,25 +120,25 @@
   <si>
     <r>
       <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="8.0"/>
       </rPr>
       <t xml:space="preserve">с {documentDate.0}г - {documentDate.1}г       </t>
     </r>
     <r>
       <rPr>
+        <sz val="8"/>
+        <color indexed="2"/>
         <rFont val="Arial"/>
-        <color rgb="FFFF0000"/>
-        <sz val="8.0"/>
       </rPr>
       <t xml:space="preserve">  </t>
     </r>
     <r>
       <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
-        <sz val="8.0"/>
       </rPr>
       <t xml:space="preserve">                                                               </t>
     </r>
@@ -145,10 +150,10 @@
     <t>{nights}</t>
   </si>
   <si>
-    <t>{organization.costPerDay}</t>
+    <t>{costPerDayFormatted}</t>
   </si>
   <si>
-    <t>{totalPrice}</t>
+    <t>{totalCost}</t>
   </si>
   <si>
     <t>Итого</t>
@@ -157,22 +162,22 @@
     <t>х</t>
   </si>
   <si>
-    <t>Сведения об использовании запасов, полученных от заказчика</t>
+    <t xml:space="preserve">Сведения об использовании запасов, полученных от заказчика</t>
   </si>
   <si>
-    <t xml:space="preserve">  ({totalPriceWords}) тенге 00 тиын</t>
+    <t xml:space="preserve">  ({totalCostRu}) тенге 00 тиын</t>
   </si>
   <si>
-    <t>наименование, количество, стоимость</t>
+    <t xml:space="preserve">наименование, количество, стоимость</t>
   </si>
   <si>
-    <t>Приложение: Перечень документации, в том числе отчет(ы) о маркетинговых, научных исследованиях, консультационных и прочих услугах (обязательны при его</t>
+    <t xml:space="preserve">Приложение: Перечень документации, в том числе отчет(ы) о маркетинговых, научных исследованиях, консультационных и прочих услугах (обязательны при его</t>
   </si>
   <si>
-    <t>(их) наличии) на _____________ страниц</t>
+    <t xml:space="preserve">(их) наличии) на _____________ страниц</t>
   </si>
   <si>
-    <t>Сдал (Исполнитель)</t>
+    <t xml:space="preserve">Сдал (Исполнитель)</t>
   </si>
   <si>
     <t>ИП</t>
@@ -184,10 +189,10 @@
     <t>/</t>
   </si>
   <si>
-    <t>Рыспаева Г.С.</t>
+    <t xml:space="preserve">Рыспаева Г.С.</t>
   </si>
   <si>
-    <t>Принял (Заказчик)</t>
+    <t xml:space="preserve">Принял (Заказчик)</t>
   </si>
   <si>
     <t>должность</t>
@@ -196,61 +201,61 @@
     <t>подпись</t>
   </si>
   <si>
-    <t>расшифровка подписи</t>
+    <t xml:space="preserve">расшифровка подписи</t>
   </si>
   <si>
     <t>М.П.</t>
   </si>
   <si>
-    <t>Дата подписания (принятия) работ (услуг)</t>
+    <t xml:space="preserve">Дата подписания (принятия) работ (услуг)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000000000"/>
   </numFmts>
   <fonts count="8">
     <font>
-      <sz val="8.0"/>
-      <color rgb="FF000000"/>
+      <sz val="8.000000"/>
+      <color indexed="64"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <i/>
-      <sz val="8.0"/>
+      <sz val="8.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font/>
     <font>
       <b/>
-      <sz val="8.0"/>
+      <sz val="8.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10.000000"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -260,239 +265,553 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="11">
-    <border/>
     <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
+      <right style="none"/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
+      <right style="none"/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
+      <right style="none"/>
+      <top style="none"/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
+      <top style="none"/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
   <cellXfs count="48">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="5" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="3" fillId="0" borderId="2" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf fontId="5" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="5" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="2" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf fontId="5" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="3" fillId="0" borderId="2" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="5" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="5" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="5" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="7" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="5" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="6" fillId="0" borderId="2" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="6" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="1" fillId="0" borderId="2" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="2" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -549,7 +868,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -575,7 +894,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -652,7 +971,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -682,33 +1001,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="16.83" defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultColWidth="16.829999999999998" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="4.5"/>
     <col customWidth="1" min="2" max="10" width="3.5"/>
-    <col customWidth="1" min="11" max="11" width="1.67"/>
+    <col customWidth="1" min="11" max="11" width="1.6699999999999999"/>
     <col customWidth="1" min="12" max="14" width="3.5"/>
-    <col customWidth="1" min="15" max="15" width="2.17"/>
-    <col customWidth="1" min="16" max="16" width="5.83"/>
-    <col customWidth="1" min="17" max="17" width="1.67"/>
+    <col customWidth="1" min="15" max="15" width="2.1699999999999999"/>
+    <col customWidth="1" min="16" max="16" width="5.8300000000000001"/>
+    <col customWidth="1" min="17" max="17" width="1.6699999999999999"/>
     <col customWidth="1" min="18" max="19" width="3.5"/>
     <col customWidth="1" min="20" max="20" width="12.33"/>
     <col customWidth="1" min="21" max="28" width="3.5"/>
     <col customWidth="1" min="29" max="29" width="4.5"/>
     <col customWidth="1" min="30" max="34" width="3.5"/>
-    <col customWidth="1" min="35" max="35" width="1.67"/>
+    <col customWidth="1" min="35" max="35" width="1.6699999999999999"/>
     <col customWidth="1" min="36" max="37" width="3.5"/>
-    <col customWidth="1" min="38" max="38" width="1.67"/>
+    <col customWidth="1" min="38" max="38" width="1.6699999999999999"/>
     <col customWidth="1" min="39" max="48" width="3.5"/>
-    <col customWidth="1" min="49" max="49" width="5.0"/>
+    <col customWidth="1" min="49" max="49" width="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="9.75" customHeight="1">
@@ -1517,7 +1838,7 @@
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
       <c r="AQ17" s="20">
-        <v>7.20128450445E11</v>
+        <v>720128450445</v>
       </c>
       <c r="AR17" s="15"/>
       <c r="AS17" s="15"/>
@@ -1711,7 +2032,7 @@
       <c r="AV21" s="31"/>
       <c r="AW21" s="31"/>
     </row>
-    <row r="22" ht="6.0" customHeight="1">
+    <row r="22" ht="6" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1825,7 +2146,7 @@
       <c r="AV23" s="15"/>
       <c r="AW23" s="16"/>
     </row>
-    <row r="24" ht="66.0" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="25"/>
       <c r="B24" s="26"/>
       <c r="C24" s="25"/>
@@ -1884,11 +2205,11 @@
     </row>
     <row r="25" ht="9.75" customHeight="1">
       <c r="A25" s="34">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="34">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
@@ -1903,14 +2224,14 @@
       <c r="N25" s="15"/>
       <c r="O25" s="16"/>
       <c r="P25" s="34">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="15"/>
       <c r="R25" s="15"/>
       <c r="S25" s="15"/>
       <c r="T25" s="16"/>
       <c r="U25" s="34">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="V25" s="15"/>
       <c r="W25" s="15"/>
@@ -1921,19 +2242,19 @@
       <c r="AB25" s="15"/>
       <c r="AC25" s="16"/>
       <c r="AD25" s="34">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="AE25" s="15"/>
       <c r="AF25" s="16"/>
       <c r="AG25" s="34">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="AH25" s="15"/>
       <c r="AI25" s="15"/>
       <c r="AJ25" s="15"/>
       <c r="AK25" s="16"/>
       <c r="AL25" s="34">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="AM25" s="15"/>
       <c r="AN25" s="15"/>
@@ -1941,7 +2262,7 @@
       <c r="AP25" s="15"/>
       <c r="AQ25" s="16"/>
       <c r="AR25" s="34">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="AS25" s="15"/>
       <c r="AT25" s="15"/>
@@ -1949,9 +2270,9 @@
       <c r="AV25" s="15"/>
       <c r="AW25" s="16"/>
     </row>
-    <row r="26" ht="24.0" customHeight="1">
+    <row r="26" ht="24" customHeight="1">
       <c r="A26" s="35">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="36" t="s">
@@ -2283,7 +2604,7 @@
       <c r="AV31" s="18"/>
       <c r="AW31" s="18"/>
     </row>
-    <row r="32" customHeight="1">
+    <row r="32">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -2491,7 +2812,7 @@
       <c r="AV35" s="1"/>
       <c r="AW35" s="1"/>
     </row>
-    <row r="36" customHeight="1">
+    <row r="36">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2780,7 +3101,7 @@
       <c r="AV40" s="1"/>
       <c r="AW40" s="1"/>
     </row>
-    <row r="41" ht="3.0" customHeight="1">
+    <row r="41" ht="3" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -51744,9 +52065,51 @@
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="AN7:AW7"/>
+    <mergeCell ref="AN8:AW8"/>
+    <mergeCell ref="AN9:AW9"/>
+    <mergeCell ref="AN10:AW10"/>
+    <mergeCell ref="A13:AJ13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:AJ15"/>
+    <mergeCell ref="AQ15:AW15"/>
+    <mergeCell ref="E16:AJ16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:AJ17"/>
+    <mergeCell ref="AQ17:AW17"/>
+    <mergeCell ref="E18:AJ18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="F19:AC19"/>
+    <mergeCell ref="AH19:AL20"/>
+    <mergeCell ref="AM19:AP20"/>
+    <mergeCell ref="A21:AG21"/>
+    <mergeCell ref="AH21:AL21"/>
+    <mergeCell ref="AM21:AP21"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:O24"/>
+    <mergeCell ref="P23:T24"/>
+    <mergeCell ref="U23:AC24"/>
+    <mergeCell ref="AD23:AF24"/>
+    <mergeCell ref="AG23:AW23"/>
+    <mergeCell ref="AG24:AK24"/>
+    <mergeCell ref="AL24:AQ24"/>
+    <mergeCell ref="AR24:AW24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:O25"/>
+    <mergeCell ref="P25:T25"/>
+    <mergeCell ref="U25:AC25"/>
+    <mergeCell ref="AD25:AF25"/>
     <mergeCell ref="AG25:AK25"/>
     <mergeCell ref="AL25:AQ25"/>
     <mergeCell ref="AR25:AW25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:O26"/>
+    <mergeCell ref="P26:T26"/>
+    <mergeCell ref="U26:AC26"/>
+    <mergeCell ref="AD26:AF26"/>
+    <mergeCell ref="AG26:AK26"/>
+    <mergeCell ref="AL26:AQ26"/>
+    <mergeCell ref="AR26:AW26"/>
     <mergeCell ref="AG27:AK27"/>
     <mergeCell ref="AL27:AQ27"/>
     <mergeCell ref="AR27:AW27"/>
@@ -51757,55 +52120,13 @@
     <mergeCell ref="L38:P38"/>
     <mergeCell ref="R38:X38"/>
     <mergeCell ref="AF38:AJ38"/>
+    <mergeCell ref="AL38:AP38"/>
     <mergeCell ref="AR38:AW38"/>
-    <mergeCell ref="AN7:AW7"/>
-    <mergeCell ref="AN8:AW8"/>
-    <mergeCell ref="AN9:AW9"/>
-    <mergeCell ref="AN10:AW10"/>
-    <mergeCell ref="A13:AJ13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="AQ15:AW15"/>
-    <mergeCell ref="E15:AJ15"/>
-    <mergeCell ref="E16:AJ16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:AJ17"/>
-    <mergeCell ref="AQ17:AW17"/>
-    <mergeCell ref="E18:AJ18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="U23:AC24"/>
-    <mergeCell ref="AD23:AF24"/>
-    <mergeCell ref="AG23:AW23"/>
-    <mergeCell ref="AG24:AK24"/>
-    <mergeCell ref="AL24:AQ24"/>
-    <mergeCell ref="AR24:AW24"/>
-    <mergeCell ref="F19:AC19"/>
-    <mergeCell ref="AH19:AL20"/>
-    <mergeCell ref="AM19:AP20"/>
-    <mergeCell ref="A21:AG21"/>
-    <mergeCell ref="AH21:AL21"/>
-    <mergeCell ref="AM21:AP21"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:O26"/>
-    <mergeCell ref="P26:T26"/>
-    <mergeCell ref="U26:AC26"/>
-    <mergeCell ref="AD26:AF26"/>
-    <mergeCell ref="AG26:AK26"/>
-    <mergeCell ref="AL26:AQ26"/>
-    <mergeCell ref="AR26:AW26"/>
-    <mergeCell ref="C23:O24"/>
-    <mergeCell ref="P23:T24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:O25"/>
-    <mergeCell ref="P25:T25"/>
-    <mergeCell ref="U25:AC25"/>
-    <mergeCell ref="AD25:AF25"/>
-    <mergeCell ref="AL38:AP38"/>
     <mergeCell ref="AL40:AQ40"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/apps/excel-service/templates/XANSHA/HOTEL/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Completed Work Certificates.xlsx
@@ -48,11 +48,11 @@
     <t>Заказчик</t>
   </si>
   <si>
-    <t xml:space="preserve">     {organization.organization}, город {organization.city}, {organization.index}, район {organization.address}
+    <t xml:space="preserve">     {customer.organization.organization}, город {customer.organization.city}, {customer.organization.index}, район {customer.organization.address}
 </t>
   </si>
   <si>
-    <t xml:space="preserve">{organization.bin} </t>
+    <t xml:space="preserve">{customer.organization.bin} </t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -220,7 +220,6 @@
   <fonts count="8">
     <font>
       <sz val="8.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -281,20 +280,20 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -302,23 +301,23 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -326,18 +325,18 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -345,40 +344,40 @@
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="none"/>

--- a/apps/excel-service/templates/XANSHA/HOTEL/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Completed Work Certificates.xlsx
@@ -48,7 +48,7 @@
     <t>Заказчик</t>
   </si>
   <si>
-    <t xml:space="preserve">     {customer.organization.organization}, город {customer.organization.city}, {customer.organization.index}, район {customer.organization.address}
+    <t xml:space="preserve">     {customer.organization.organization}, город {customer.organization.city}, {customer.organization.index} район {customer.organization.address}
 </t>
   </si>
   <si>

--- a/apps/excel-service/templates/XANSHA/HOTEL/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Completed Work Certificates.xlsx
@@ -1008,7 +1008,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr defaultColWidth="16.829999999999998" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -52124,8 +52124,8 @@
     <mergeCell ref="AL40:AQ40"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="91" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/apps/excel-service/templates/XANSHA/HOTEL/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Completed Work Certificates.xlsx
@@ -165,7 +165,7 @@
     <t xml:space="preserve">Сведения об использовании запасов, полученных от заказчика</t>
   </si>
   <si>
-    <t xml:space="preserve">  ({totalCostRu}) тенге 00 тиын</t>
+    <t xml:space="preserve">  ({totalCostRu}) тенге{totalCostCentsRu} тиын</t>
   </si>
   <si>
     <t xml:space="preserve">наименование, количество, стоимость</t>
